--- a/Assets/Config/Excel/物品配置.xlsx
+++ b/Assets/Config/Excel/物品配置.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Projects\Joker_MMO\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F527A2-EF2C-421D-A7B6-C7444F640957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7981221E-E14D-40E9-9601-4BDAC8F4DD34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30480" yWindow="4140" windowWidth="23040" windowHeight="12120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6648" yWindow="348" windowWidth="23040" windowHeight="13560" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="装备" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="63">
   <si>
     <t>Key</t>
   </si>
@@ -67,139 +67,178 @@
     <t>It's a low-level weapon, but it's still powerful！</t>
   </si>
   <si>
+    <t>血刀</t>
+  </si>
+  <si>
+    <t>Blood Sword</t>
+  </si>
+  <si>
+    <t>强力的武器！</t>
+  </si>
+  <si>
+    <t>A powerful weapon!</t>
+  </si>
+  <si>
+    <t>恢复血量</t>
+  </si>
+  <si>
+    <t>Consumable_0</t>
+  </si>
+  <si>
+    <t>小瓶药剂</t>
+  </si>
+  <si>
+    <t>Vial Potions</t>
+  </si>
+  <si>
+    <t>恢复一定的生命值！</t>
+  </si>
+  <si>
+    <t>Restore health!</t>
+  </si>
+  <si>
+    <t>Consumable_1</t>
+  </si>
+  <si>
+    <t>中瓶药剂</t>
+  </si>
+  <si>
+    <t>Medium Potions</t>
+  </si>
+  <si>
+    <t>恢复一定的生命值</t>
+  </si>
+  <si>
+    <t>Restore health</t>
+  </si>
+  <si>
+    <t>Consumable_2</t>
+  </si>
+  <si>
+    <t>大瓶药剂</t>
+  </si>
+  <si>
+    <t>Large Potions</t>
+  </si>
+  <si>
+    <t>Consumable_3</t>
+  </si>
+  <si>
+    <t>超大瓶药剂</t>
+  </si>
+  <si>
+    <t>Supervial Potions</t>
+  </si>
+  <si>
+    <t>Consumable_4</t>
+  </si>
+  <si>
+    <t>终极药剂</t>
+  </si>
+  <si>
+    <t>Ultimate Potion</t>
+  </si>
+  <si>
+    <t>牙齿</t>
+  </si>
+  <si>
+    <t>Tooth</t>
+  </si>
+  <si>
+    <t>可以用来制作一些药剂</t>
+  </si>
+  <si>
+    <t>It can be used to make some kind of potion</t>
+  </si>
+  <si>
+    <t>Material_1</t>
+  </si>
+  <si>
+    <t>眼睛</t>
+  </si>
+  <si>
+    <t>Eye</t>
+  </si>
+  <si>
+    <t>Material_2</t>
+  </si>
+  <si>
+    <t>红宝石</t>
+  </si>
+  <si>
+    <t>Ruby</t>
+  </si>
+  <si>
+    <t>树叶</t>
+  </si>
+  <si>
+    <t>Leaf</t>
+  </si>
+  <si>
+    <t>Weapon_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_WeaponSlot</t>
+  </si>
+  <si>
+    <t>UI_MaterialSlot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_ConsumableSlot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SlotKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Price</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合成配方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material_0,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Weapon_1</t>
-  </si>
-  <si>
-    <t>血刀</t>
-  </si>
-  <si>
-    <t>Blood Sword</t>
-  </si>
-  <si>
-    <t>强力的武器！</t>
-  </si>
-  <si>
-    <t>A powerful weapon!</t>
-  </si>
-  <si>
-    <t>恢复血量</t>
-  </si>
-  <si>
-    <t>Consumable_0</t>
-  </si>
-  <si>
-    <t>小瓶药剂</t>
-  </si>
-  <si>
-    <t>Vial Potions</t>
-  </si>
-  <si>
-    <t>恢复一定的生命值！</t>
-  </si>
-  <si>
-    <t>Restore health!</t>
-  </si>
-  <si>
-    <t>Consumable_1</t>
-  </si>
-  <si>
-    <t>中瓶药剂</t>
-  </si>
-  <si>
-    <t>Medium Potions</t>
-  </si>
-  <si>
-    <t>恢复一定的生命值</t>
-  </si>
-  <si>
-    <t>Restore health</t>
-  </si>
-  <si>
-    <t>Consumable_2</t>
-  </si>
-  <si>
-    <t>大瓶药剂</t>
-  </si>
-  <si>
-    <t>Large Potions</t>
-  </si>
-  <si>
-    <t>Consumable_3</t>
-  </si>
-  <si>
-    <t>超大瓶药剂</t>
-  </si>
-  <si>
-    <t>Supervial Potions</t>
-  </si>
-  <si>
-    <t>Consumable_4</t>
-  </si>
-  <si>
-    <t>终极药剂</t>
-  </si>
-  <si>
-    <t>Ultimate Potion</t>
-  </si>
-  <si>
-    <t>Material_0</t>
-  </si>
-  <si>
-    <t>牙齿</t>
-  </si>
-  <si>
-    <t>Tooth</t>
-  </si>
-  <si>
-    <t>可以用来制作一些药剂</t>
-  </si>
-  <si>
-    <t>It can be used to make some kind of potion</t>
-  </si>
-  <si>
-    <t>Material_1</t>
-  </si>
-  <si>
-    <t>眼睛</t>
-  </si>
-  <si>
-    <t>Eye</t>
-  </si>
-  <si>
-    <t>Material_2</t>
-  </si>
-  <si>
-    <t>红宝石</t>
-  </si>
-  <si>
-    <t>Ruby</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_0,1,Material_1,1,Material_0,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Material_3</t>
-  </si>
-  <si>
-    <t>树叶</t>
-  </si>
-  <si>
-    <t>Leaf</t>
-  </si>
-  <si>
-    <t>Weapon_0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI_WeaponSlot</t>
-  </si>
-  <si>
-    <t>UI_MaterialSlot</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI_ConsumableSlot</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SlotKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consumable_0,1,Material_2,1,Material_3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consumable_1,1,Material_2,1,Material_3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consumable_3,1,Material_2,1,Material_1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consumable_2,1,Material_2,1,Material_1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material_2,1,Material_0,1,Material_3,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -527,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.44140625" customWidth="1"/>
@@ -535,9 +574,10 @@
     <col min="3" max="3" width="16.44140625" customWidth="1"/>
     <col min="4" max="4" width="50.33203125" customWidth="1"/>
     <col min="7" max="7" width="18.109375" customWidth="1"/>
+    <col min="9" max="9" width="53" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -557,12 +597,18 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
@@ -580,30 +626,42 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2">
+        <v>100</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
       </c>
       <c r="F3">
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>50</v>
+        <v>47</v>
+      </c>
+      <c r="H3">
+        <v>200</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -615,7 +673,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.44140625" customWidth="1"/>
@@ -623,9 +681,11 @@
     <col min="5" max="5" width="21.88671875" customWidth="1"/>
     <col min="6" max="6" width="17.33203125" customWidth="1"/>
     <col min="7" max="7" width="22.88671875" customWidth="1"/>
+    <col min="9" max="9" width="42.109375" customWidth="1"/>
+    <col min="10" max="10" width="25.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -642,125 +702,161 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
       </c>
       <c r="F2">
         <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
       </c>
       <c r="F3">
         <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="H3">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
         <v>26</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
       <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
         <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
       </c>
       <c r="F4">
         <v>30</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="H4">
+        <v>30</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
         <v>29</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>30</v>
       </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
       <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
         <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
       </c>
       <c r="F5">
         <v>40</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="H5">
+        <v>40</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
       <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
         <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
       </c>
       <c r="F6">
         <v>50</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
+      </c>
+      <c r="H6">
+        <v>50</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -772,7 +868,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.6640625" customWidth="1"/>
@@ -782,7 +878,7 @@
     <col min="10" max="10" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -799,87 +895,105 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
         <v>35</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>36</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>37</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>38</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B3" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
         <v>40</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>41</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
         <v>42</v>
       </c>
-      <c r="D3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C4" t="s">
         <v>43</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" t="s">
         <v>44</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>45</v>
       </c>
-      <c r="D4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>51</v>
+      <c r="G5">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
